--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="362">
   <si>
     <t>FEATURE</t>
   </si>
@@ -78,16 +78,16 @@
     <t>Dashboard-001</t>
   </si>
   <si>
+    <t>2026-09-21 13:21:57</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>verify-dashboard-with-tab</t>
   </si>
   <si>
     <t>DashBoard-002</t>
-  </si>
-  <si>
-    <t>2026-09-21 12:42:50</t>
-  </si>
-  <si>
-    <t>PASS</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1111,6 +1111,9 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
+    <t>Passed in 3.4s on chromium.</t>
+  </si>
+  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1131,6 +1134,9 @@
   </si>
   <si>
     <t>User remains on /select-location awaiting a location choice</t>
+  </si>
+  <si>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Dashboard-001-AC3-POS-01</t>
@@ -1160,25 +1166,19 @@
     <t>User is on the inventory-vendors dashboard</t>
   </si>
   <si>
+    <t>Passed in 5.4s on chromium.</t>
+  </si>
+  <si>
     <t>DashBoard-002-AC1-POS-01</t>
   </si>
   <si>
-    <t>Passed in 3.2s on chromium.</t>
-  </si>
-  <si>
     <t>DashBoard-002-AC2-POS-01</t>
   </si>
   <si>
-    <t>Passed in 2.8s on chromium.</t>
-  </si>
-  <si>
     <t>DashBoard-002-AC3-POS-01</t>
   </si>
   <si>
     <t>User is on the inventory-vendors dashboard (Inventory sub-view by default)</t>
-  </si>
-  <si>
-    <t>Passed in 6.3s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC4-POS-01</t>
@@ -1207,9 +1207,6 @@
   </si>
   <si>
     <t>User is working in the Inventory section of the dashboard</t>
-  </si>
-  <si>
-    <t>Passed in 6.0s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -1833,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1842,18 +1839,18 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1865,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1874,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1897,7 +1894,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -3726,74 +3723,74 @@
         <v>331</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>332</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>340</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>349</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3853,7 +3850,7 @@
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>326</v>
@@ -3877,74 +3874,74 @@
         <v>331</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -3973,10 +3970,10 @@
         <v>361</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="357">
   <si>
     <t>FEATURE</t>
   </si>
@@ -76,12 +76,6 @@
   </si>
   <si>
     <t>Dashboard-001</t>
-  </si>
-  <si>
-    <t>2026-09-21 13:21:57</t>
-  </si>
-  <si>
-    <t>PASS</t>
   </si>
   <si>
     <t>verify-dashboard-with-tab</t>
@@ -1111,9 +1105,6 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
-    <t>Passed in 3.4s on chromium.</t>
-  </si>
-  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1134,9 +1125,6 @@
   </si>
   <si>
     <t>User remains on /select-location awaiting a location choice</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>Dashboard-001-AC3-POS-01</t>
@@ -1164,9 +1152,6 @@
   </si>
   <si>
     <t>User is on the inventory-vendors dashboard</t>
-  </si>
-  <si>
-    <t>Passed in 5.4s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC1-POS-01</t>
@@ -1213,7 +1198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1239,12 +1224,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1255,7 +1234,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1270,11 +1249,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1315,7 +1289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1327,12 +1301,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1830,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1839,18 +1810,18 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1878,35 +1849,35 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4">
         <v>56</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>36</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>20</v>
       </c>
-      <c r="F7" s="5">
-        <v>3</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="5">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>25</v>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1934,63 +1905,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1998,31 +1969,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2030,31 +2001,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2062,31 +2033,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2094,31 +2065,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2126,31 +2097,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2158,31 +2129,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2190,31 +2161,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2222,31 +2193,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2254,31 +2225,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2286,31 +2257,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2318,63 +2289,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="H13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2382,31 +2353,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2414,31 +2385,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2446,127 +2417,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2574,97 +2545,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2693,63 +2664,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -2780,63 +2751,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -2844,31 +2815,31 @@
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2876,31 +2847,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2908,63 +2879,63 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2972,31 +2943,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -3004,95 +2975,95 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -3100,31 +3071,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3132,63 +3103,63 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -3196,31 +3167,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -3228,63 +3199,63 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3292,63 +3263,63 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3356,31 +3327,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3388,159 +3359,159 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>291</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3548,97 +3519,97 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3667,130 +3638,130 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>21</v>
+        <v>42</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>21</v>
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>21</v>
+        <v>42</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3818,63 +3789,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3882,31 +3853,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3914,31 +3885,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3946,31 +3917,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="386">
   <si>
     <t>FEATURE</t>
   </si>
@@ -54,16 +54,22 @@
     <t>Login</t>
   </si>
   <si>
+    <t>2026-09-22 15:52:14</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>order-flow</t>
+  </si>
+  <si>
+    <t>Order-01</t>
+  </si>
+  <si>
     <t>never</t>
   </si>
   <si>
     <t>NOT RUN</t>
-  </si>
-  <si>
-    <t>order-flow</t>
-  </si>
-  <si>
-    <t>Order-01</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -148,7 +154,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -178,6 +184,9 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
+    <t>Passed in 4.1s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -196,6 +205,9 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
+    <t>Passed in 3.1s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -220,6 +232,9 @@
     <t>User remains on /Login</t>
   </si>
   <si>
+    <t>Passed in 13.0s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -238,6 +253,9 @@
 Password: (empty)</t>
   </si>
   <si>
+    <t>Passed in 12.3s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -255,6 +273,9 @@
 Password: (empty)</t>
   </si>
   <si>
+    <t>Passed in 12.2s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
@@ -275,6 +296,9 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
+    <t>Passed in 14.9s on chromium.</t>
+  </si>
+  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -292,6 +316,9 @@
 Password: Whatever!2025</t>
   </si>
   <si>
+    <t>Passed in 12.7s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -308,6 +335,9 @@
   </si>
   <si>
     <t>Password input has attribute type='password'</t>
+  </si>
+  <si>
+    <t>Passed in 2.6s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -330,6 +360,9 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
+    <t>Passed in 14.4s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -349,6 +382,9 @@
     <t>User signed in</t>
   </si>
   <si>
+    <t>Passed in 3.0s on chromium.</t>
+  </si>
+  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -385,6 +421,9 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
+    <t>Passed in 4.7s on chromium.</t>
+  </si>
+  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -400,6 +439,9 @@
     <t>User on the signup screen</t>
   </si>
   <si>
+    <t>Passed in 2.7s on chromium.</t>
+  </si>
+  <si>
     <t>Login-NAV-03</t>
   </si>
   <si>
@@ -413,6 +455,9 @@
   </si>
   <si>
     <t>User on homepage</t>
+  </si>
+  <si>
+    <t>Passed in 4.2s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -580,6 +625,9 @@
     <t>5 new 'Submitted' vendor orders exist in /order-history</t>
   </si>
   <si>
+    <t>No run data — execute the suite to capture the actual result.</t>
+  </si>
+  <si>
     <t>SignUp-001-AC1-POS-01</t>
   </si>
   <si>
@@ -663,6 +711,9 @@
     <t>User remains on step 1</t>
   </si>
   <si>
+    <t>Passed in 5.6s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-02</t>
   </si>
   <si>
@@ -693,6 +744,9 @@
   </si>
   <si>
     <t>Business Email: (empty)</t>
+  </si>
+  <si>
+    <t>Passed in 17.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-04</t>
@@ -777,6 +831,9 @@
   </si>
   <si>
     <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
+  </si>
+  <si>
+    <t>Passed in 15.7s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -807,6 +864,9 @@
     <t>User remains on step 2</t>
   </si>
   <si>
+    <t>Passed in 17.7s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NEG-09</t>
   </si>
   <si>
@@ -849,6 +909,9 @@
     <t>Create Account button is disabled</t>
   </si>
   <si>
+    <t>Passed in 18.8s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-UI-01</t>
   </si>
   <si>
@@ -862,6 +925,9 @@
   </si>
   <si>
     <t>All three have the readonly attribute</t>
+  </si>
+  <si>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -898,6 +964,9 @@
 3. Click again to re-mask</t>
   </si>
   <si>
+    <t>Passed in 4.0s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-UI-04</t>
   </si>
   <si>
@@ -938,7 +1007,13 @@
     <t>User on the login screen</t>
   </si>
   <si>
+    <t>Passed in 3.2s on chromium.</t>
+  </si>
+  <si>
     <t>SignUp-001-NAV-02</t>
+  </si>
+  <si>
+    <t>Passed in 2.5s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1105,6 +1180,9 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
+    <t>Passed in 4.9s on chromium.</t>
+  </si>
+  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1154,6 +1232,9 @@
     <t>User is on the inventory-vendors dashboard</t>
   </si>
   <si>
+    <t>Passed in 22.7s on chromium.</t>
+  </si>
+  <si>
     <t>DashBoard-002-AC1-POS-01</t>
   </si>
   <si>
@@ -1164,6 +1245,9 @@
   </si>
   <si>
     <t>User is on the inventory-vendors dashboard (Inventory sub-view by default)</t>
+  </si>
+  <si>
+    <t>Passed in 6.4s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC4-POS-01</t>
@@ -1192,13 +1276,16 @@
   </si>
   <si>
     <t>User is working in the Inventory section of the dashboard</t>
+  </si>
+  <si>
+    <t>Passed in 9.5s on chromium.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1214,6 +1301,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1234,7 +1327,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1244,6 +1337,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1289,7 +1387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1301,9 +1399,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1705,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1746,18 +1847,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
         <v>26</v>
@@ -1769,7 +1870,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1786,10 +1887,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1801,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1818,10 +1919,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1833,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1849,35 +1950,35 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5">
         <v>56</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>36</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>20</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>23</v>
+      <c r="I7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1905,63 +2006,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1969,31 +2070,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2001,31 +2102,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2033,31 +2134,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2065,31 +2166,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2097,31 +2198,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2129,31 +2230,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2161,31 +2262,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2193,31 +2294,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2225,31 +2326,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2257,31 +2358,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2289,63 +2390,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2353,31 +2454,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2385,31 +2486,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2417,127 +2518,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2545,97 +2646,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2664,66 +2765,66 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2751,127 +2852,127 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>184</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2879,63 +2980,63 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2943,31 +3044,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2975,95 +3076,95 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -3071,31 +3172,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>256</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3103,63 +3204,63 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>42</v>
+        <v>270</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -3167,31 +3268,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>42</v>
+        <v>276</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -3199,63 +3300,63 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3263,63 +3364,63 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
+        <v>301</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3327,31 +3428,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>42</v>
+        <v>303</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3359,159 +3460,159 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3519,97 +3620,97 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3638,63 +3739,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>355</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3702,31 +3803,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3734,31 +3835,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>371</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3789,63 +3890,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3853,31 +3954,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3885,31 +3986,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
+        <v>376</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3917,31 +4018,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
+        <v>385</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="385">
   <si>
     <t>FEATURE</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-09-22 15:52:14</t>
+    <t>2026-09-22 15:58:11</t>
   </si>
   <si>
     <t>PASS</t>
@@ -154,7 +154,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 3.6s on chromium.</t>
+    <t>Passed in 4.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -184,7 +184,7 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 4.1s on chromium.</t>
+    <t>Passed in 7.1s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -205,7 +205,7 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 3.1s on chromium.</t>
+    <t>Passed in 3.9s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-03</t>
@@ -232,7 +232,7 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 13.0s on chromium.</t>
+    <t>Passed in 14.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-04</t>
@@ -253,7 +253,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 12.3s on chromium.</t>
+    <t>Passed in 13.7s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-05</t>
@@ -273,7 +273,7 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 12.2s on chromium.</t>
+    <t>Passed in 13.4s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-06</t>
@@ -296,7 +296,7 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 14.9s on chromium.</t>
+    <t>Passed in 18.5s on chromium.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-07</t>
@@ -316,7 +316,7 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 12.7s on chromium.</t>
+    <t>Passed in 17.3s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-01</t>
@@ -337,7 +337,7 @@
     <t>Password input has attribute type='password'</t>
   </si>
   <si>
-    <t>Passed in 2.6s on chromium.</t>
+    <t>Passed in 9.1s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -360,7 +360,7 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 14.4s on chromium.</t>
+    <t>Passed in 3.2s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-03</t>
@@ -382,7 +382,7 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 3.0s on chromium.</t>
+    <t>Passed in 5.7s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-04</t>
@@ -421,7 +421,7 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 4.7s on chromium.</t>
+    <t>Passed in 2.7s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-02</t>
@@ -439,7 +439,7 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 2.7s on chromium.</t>
+    <t>Passed in 2.5s on chromium.</t>
   </si>
   <si>
     <t>Login-NAV-03</t>
@@ -457,7 +457,7 @@
     <t>User on homepage</t>
   </si>
   <si>
-    <t>Passed in 4.2s on chromium.</t>
+    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -711,7 +711,7 @@
     <t>User remains on step 1</t>
   </si>
   <si>
-    <t>Passed in 5.6s on chromium.</t>
+    <t>Passed in 5.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-02</t>
@@ -746,7 +746,7 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Passed in 17.8s on chromium.</t>
+    <t>Passed in 14.3s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-04</t>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>Email field reports HTML5 typeMismatch; form does not advance</t>
+  </si>
+  <si>
+    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-05</t>
@@ -833,7 +836,7 @@
     <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
   </si>
   <si>
-    <t>Passed in 15.7s on chromium.</t>
+    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -864,9 +867,6 @@
     <t>User remains on step 2</t>
   </si>
   <si>
-    <t>Passed in 17.7s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-09</t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>Create Account button is disabled</t>
   </si>
   <si>
-    <t>Passed in 18.8s on chromium.</t>
+    <t>Passed in 6.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-01</t>
@@ -927,7 +927,7 @@
     <t>All three have the readonly attribute</t>
   </si>
   <si>
-    <t>Passed in 2.9s on chromium.</t>
+    <t>Passed in 15.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -964,7 +964,7 @@
 3. Click again to re-mask</t>
   </si>
   <si>
-    <t>Passed in 4.0s on chromium.</t>
+    <t>Passed in 3.6s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-04</t>
@@ -1007,13 +1007,10 @@
     <t>User on the login screen</t>
   </si>
   <si>
-    <t>Passed in 3.2s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NAV-02</t>
   </si>
   <si>
-    <t>Passed in 2.5s on chromium.</t>
+    <t>Passed in 4.5s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1180,7 +1177,7 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
-    <t>Passed in 4.9s on chromium.</t>
+    <t>Passed in 4.4s on chromium.</t>
   </si>
   <si>
     <t>Dashboard-001-AC2-POS-01</t>
@@ -1203,6 +1200,9 @@
   </si>
   <si>
     <t>User remains on /select-location awaiting a location choice</t>
+  </si>
+  <si>
+    <t>Passed in 10.5s on chromium.</t>
   </si>
   <si>
     <t>Dashboard-001-AC3-POS-01</t>
@@ -1232,7 +1232,7 @@
     <t>User is on the inventory-vendors dashboard</t>
   </si>
   <si>
-    <t>Passed in 22.7s on chromium.</t>
+    <t>Passed in 4.8s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC1-POS-01</t>
@@ -1245,9 +1245,6 @@
   </si>
   <si>
     <t>User is on the inventory-vendors dashboard (Inventory sub-view by default)</t>
-  </si>
-  <si>
-    <t>Passed in 6.4s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC4-POS-01</t>
@@ -1278,7 +1275,7 @@
     <t>User is working in the Inventory section of the dashboard</t>
   </si>
   <si>
-    <t>Passed in 9.5s on chromium.</t>
+    <t>Passed in 5.3s on chromium.</t>
   </si>
 </sst>
 </file>
@@ -3068,7 +3065,7 @@
         <v>208</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -3076,25 +3073,25 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>208</v>
@@ -3108,28 +3105,28 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>119</v>
@@ -3140,31 +3137,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -3172,31 +3169,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3213,7 +3210,7 @@
         <v>259</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>260</v>
@@ -3225,7 +3222,7 @@
         <v>262</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>119</v>
@@ -3257,7 +3254,7 @@
         <v>269</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>270</v>
@@ -3341,7 +3338,7 @@
         <v>285</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>286</v>
@@ -3420,7 +3417,7 @@
         <v>300</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>301</v>
+        <v>138</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3428,7 +3425,7 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>296</v>
@@ -3452,7 +3449,7 @@
         <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3460,25 +3457,25 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>97</v>
@@ -3492,25 +3489,25 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>97</v>
@@ -3524,25 +3521,25 @@
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>97</v>
@@ -3556,28 +3553,28 @@
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>119</v>
@@ -3588,25 +3585,25 @@
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>97</v>
@@ -3620,25 +3617,25 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>97</v>
@@ -3652,25 +3649,25 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>204</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>97</v>
@@ -3684,28 +3681,28 @@
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>119</v>
@@ -3771,31 +3768,31 @@
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3803,31 +3800,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3925,28 +3922,28 @@
         <v>372</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3957,28 +3954,28 @@
         <v>373</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -4010,7 +4007,7 @@
         <v>375</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>376</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -4018,31 +4015,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="357">
   <si>
     <t>FEATURE</t>
   </si>
@@ -54,22 +54,16 @@
     <t>Login</t>
   </si>
   <si>
-    <t>2026-09-22 15:58:11</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>never</t>
+  </si>
+  <si>
+    <t>NOT RUN</t>
   </si>
   <si>
     <t>order-flow</t>
   </si>
   <si>
     <t>Order-01</t>
-  </si>
-  <si>
-    <t>never</t>
-  </si>
-  <si>
-    <t>NOT RUN</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -154,7 +148,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>Passed in 4.1s on chromium.</t>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -184,9 +178,6 @@
     <t>User NOT authenticated</t>
   </si>
   <si>
-    <t>Passed in 7.1s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-02</t>
   </si>
   <si>
@@ -205,9 +196,6 @@
 Password: AnyPass!1234</t>
   </si>
   <si>
-    <t>Passed in 3.9s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-03</t>
   </si>
   <si>
@@ -232,9 +220,6 @@
     <t>User remains on /Login</t>
   </si>
   <si>
-    <t>Passed in 14.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-04</t>
   </si>
   <si>
@@ -253,9 +238,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 13.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-05</t>
   </si>
   <si>
@@ -273,9 +255,6 @@
 Password: (empty)</t>
   </si>
   <si>
-    <t>Passed in 13.4s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-06</t>
   </si>
   <si>
@@ -296,9 +275,6 @@
     <t>Email field reports HTML5 typeMismatch validity; no redirect</t>
   </si>
   <si>
-    <t>Passed in 18.5s on chromium.</t>
-  </si>
-  <si>
     <t>Login-AC1-NEG-07</t>
   </si>
   <si>
@@ -316,9 +292,6 @@
 Password: Whatever!2025</t>
   </si>
   <si>
-    <t>Passed in 17.3s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-01</t>
   </si>
   <si>
@@ -335,9 +308,6 @@
   </si>
   <si>
     <t>Password input has attribute type='password'</t>
-  </si>
-  <si>
-    <t>Passed in 9.1s on chromium.</t>
   </si>
   <si>
     <t>Login-UI-02</t>
@@ -360,9 +330,6 @@
     <t>Click 1: type='text'; click 2: type='password'</t>
   </si>
   <si>
-    <t>Passed in 3.2s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-03</t>
   </si>
   <si>
@@ -382,9 +349,6 @@
     <t>User signed in</t>
   </si>
   <si>
-    <t>Passed in 5.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-UI-04</t>
   </si>
   <si>
@@ -421,9 +385,6 @@
     <t>User on the forgot-password screen</t>
   </si>
   <si>
-    <t>Passed in 2.7s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-02</t>
   </si>
   <si>
@@ -439,9 +400,6 @@
     <t>User on the signup screen</t>
   </si>
   <si>
-    <t>Passed in 2.5s on chromium.</t>
-  </si>
-  <si>
     <t>Login-NAV-03</t>
   </si>
   <si>
@@ -455,9 +413,6 @@
   </si>
   <si>
     <t>User on homepage</t>
-  </si>
-  <si>
-    <t>Passed in 4.0s on chromium.</t>
   </si>
   <si>
     <t>Login-EDGE-01</t>
@@ -625,9 +580,6 @@
     <t>5 new 'Submitted' vendor orders exist in /order-history</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
-  </si>
-  <si>
     <t>SignUp-001-AC1-POS-01</t>
   </si>
   <si>
@@ -711,9 +663,6 @@
     <t>User remains on step 1</t>
   </si>
   <si>
-    <t>Passed in 5.8s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-02</t>
   </si>
   <si>
@@ -746,9 +695,6 @@
     <t>Business Email: (empty)</t>
   </si>
   <si>
-    <t>Passed in 14.3s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-NEG-04</t>
   </si>
   <si>
@@ -766,9 +712,6 @@
   </si>
   <si>
     <t>Email field reports HTML5 typeMismatch; form does not advance</t>
-  </si>
-  <si>
-    <t>Passed in 2.9s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-05</t>
@@ -834,9 +777,6 @@
   </si>
   <si>
     <t>Subdomain ∈ /^[a-z0-9-]+$/; contains 'my' + 'eatery'</t>
-  </si>
-  <si>
-    <t>Passed in 3.8s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-NEG-08</t>
@@ -909,9 +849,6 @@
     <t>Create Account button is disabled</t>
   </si>
   <si>
-    <t>Passed in 6.8s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-01</t>
   </si>
   <si>
@@ -925,9 +862,6 @@
   </si>
   <si>
     <t>All three have the readonly attribute</t>
-  </si>
-  <si>
-    <t>Passed in 15.4s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-UI-02</t>
@@ -964,9 +898,6 @@
 3. Click again to re-mask</t>
   </si>
   <si>
-    <t>Passed in 3.6s on chromium.</t>
-  </si>
-  <si>
     <t>SignUp-001-UI-04</t>
   </si>
   <si>
@@ -1008,9 +939,6 @@
   </si>
   <si>
     <t>SignUp-001-NAV-02</t>
-  </si>
-  <si>
-    <t>Passed in 4.5s on chromium.</t>
   </si>
   <si>
     <t>SignUp-001-EDGE-01</t>
@@ -1177,9 +1105,6 @@
     <t>User authenticated; session established</t>
   </si>
   <si>
-    <t>Passed in 4.4s on chromium.</t>
-  </si>
-  <si>
     <t>Dashboard-001-AC2-POS-01</t>
   </si>
   <si>
@@ -1200,9 +1125,6 @@
   </si>
   <si>
     <t>User remains on /select-location awaiting a location choice</t>
-  </si>
-  <si>
-    <t>Passed in 10.5s on chromium.</t>
   </si>
   <si>
     <t>Dashboard-001-AC3-POS-01</t>
@@ -1230,9 +1152,6 @@
   </si>
   <si>
     <t>User is on the inventory-vendors dashboard</t>
-  </si>
-  <si>
-    <t>Passed in 4.8s on chromium.</t>
   </si>
   <si>
     <t>DashBoard-002-AC1-POS-01</t>
@@ -1273,16 +1192,13 @@
   </si>
   <si>
     <t>User is working in the Inventory section of the dashboard</t>
-  </si>
-  <si>
-    <t>Passed in 5.3s on chromium.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1298,12 +1214,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF155724"/>
-      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1324,7 +1234,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1334,11 +1244,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1384,7 +1289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1396,12 +1301,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1803,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1844,18 +1746,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>26</v>
@@ -1867,7 +1769,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -1884,10 +1786,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1899,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -1916,10 +1818,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1931,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -1947,35 +1849,35 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4">
         <v>56</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>36</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>20</v>
       </c>
-      <c r="F7" s="5">
-        <v>33</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="5">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>25</v>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2003,63 +1905,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -2067,31 +1969,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -2099,31 +2001,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2131,31 +2033,31 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>
@@ -2163,31 +2065,31 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -2195,31 +2097,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -2227,31 +2129,31 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>13</v>
@@ -2259,31 +2161,31 @@
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>13</v>
@@ -2291,31 +2193,31 @@
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -2323,31 +2225,31 @@
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -2355,31 +2257,31 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>13</v>
@@ -2387,63 +2289,63 @@
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -2451,31 +2353,31 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>13</v>
@@ -2483,31 +2385,31 @@
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -2515,127 +2417,127 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>13</v>
@@ -2643,97 +2545,97 @@
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2762,66 +2664,66 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2849,127 +2751,127 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>209</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -2977,63 +2879,63 @@
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>220</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>13</v>
@@ -3041,31 +2943,31 @@
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>13</v>
@@ -3073,95 +2975,95 @@
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>248</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>13</v>
@@ -3169,31 +3071,31 @@
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>248</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>13</v>
@@ -3201,63 +3103,63 @@
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>270</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>13</v>
@@ -3265,31 +3167,31 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>276</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>13</v>
@@ -3297,63 +3199,63 @@
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>13</v>
@@ -3361,63 +3263,63 @@
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>13</v>
@@ -3425,31 +3327,31 @@
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>302</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>13</v>
@@ -3457,159 +3359,159 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J22" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J23" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>287</v>
+        <v>42</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>13</v>
@@ -3617,97 +3519,97 @@
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J26" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J27" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3736,63 +3638,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3800,31 +3702,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>362</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3832,31 +3734,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>371</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -3887,63 +3789,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -3951,31 +3853,31 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>356</v>
+        <v>331</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>248</v>
+        <v>42</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -3983,31 +3885,31 @@
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>13</v>
@@ -4015,31 +3917,31 @@
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>384</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>13</v>

--- a/reports/Test-Cases-moontower.xlsx
+++ b/reports/Test-Cases-moontower.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="360">
   <si>
     <t>FEATURE</t>
   </si>
@@ -54,16 +54,22 @@
     <t>Login</t>
   </si>
   <si>
+    <t>2026-09-22 17:47:16</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>order-flow</t>
+  </si>
+  <si>
+    <t>Order-01</t>
+  </si>
+  <si>
     <t>never</t>
   </si>
   <si>
     <t>NOT RUN</t>
-  </si>
-  <si>
-    <t>order-flow</t>
-  </si>
-  <si>
-    <t>Order-01</t>
   </si>
   <si>
     <t>user-signup</t>
@@ -148,7 +154,7 @@
     <t>User authenticated; session cookie set</t>
   </si>
   <si>
-    <t>No run data — execute the suite to capture the actual result.</t>
+    <t>Passed in 4.3s on galaxy-s24.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-01</t>
@@ -176,6 +182,9 @@
   </si>
   <si>
     <t>User NOT authenticated</t>
+  </si>
+  <si>
+    <t>No run data — execute the suite to capture the actual result.</t>
   </si>
   <si>
     <t>Login-AC1-NEG-02</t>
@@ -1198,7 +1207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1214,6 +1223,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF155724"/>
+      <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1234,7 +1249,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1244,6 +1259,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2A8FB8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1289,7 +1309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1301,9 +1321,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1705,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
@@ -1746,18 +1769,18 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2">
         <v>26</v>
@@ -1778,18 +1801,18 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -1810,18 +1833,18 @@
         <v>0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -1842,42 +1865,42 @@
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5">
         <v>56</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>36</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>20</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="H7" s="5">
         <v>0</v>
       </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>23</v>
+      <c r="I7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1905,63 +1928,63 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>13</v>
@@ -1969,673 +1992,673 @@
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J18" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2664,66 +2687,66 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="240" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2751,865 +2774,865 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J20" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J26" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J27" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3638,130 +3661,130 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3789,162 +3812,162 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
